--- a/htr-FHIR/ig/ValueSet-fr-core-participation-type.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-core-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
